--- a/source/8、绩效异常岗位/4、供件岗/供件岗-5月.xlsx
+++ b/source/8、绩效异常岗位/4、供件岗/供件岗-5月.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3042" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3270" uniqueCount="167">
   <si>
     <t>数据日期</t>
   </si>
@@ -515,6 +515,21 @@
   </si>
   <si>
     <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>109.1</t>
+  </si>
+  <si>
+    <t>临海</t>
+  </si>
+  <si>
+    <t>96.2</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
   </si>
 </sst>
 </file>
@@ -1448,7 +1463,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H663"/>
+  <dimension ref="A1:H711"/>
   <sheetFormatPr defaultColWidth="12.6363636363636" defaultRowHeight="20" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="16384" width="12.6363636363636" style="1" customWidth="1"/>
@@ -18690,6 +18705,1254 @@
       </c>
       <c r="H663" s="1">
         <v>12.2</v>
+      </c>
+    </row>
+    <row r="664" customHeight="1" spans="1:8">
+      <c r="A664" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B664" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C664" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D664" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E664" s="1">
+        <v>73.6</v>
+      </c>
+      <c r="F664" s="1">
+        <v>19.6</v>
+      </c>
+      <c r="G664" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H664" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="665" customHeight="1" spans="1:8">
+      <c r="A665" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B665" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C665" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D665" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E665" s="1">
+        <v>47.6</v>
+      </c>
+      <c r="F665" s="1">
+        <v>18.3</v>
+      </c>
+      <c r="G665" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H665" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="666" customHeight="1" spans="1:8">
+      <c r="A666" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B666" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C666" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D666" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E666" s="1">
+        <v>88.8</v>
+      </c>
+      <c r="F666" s="1">
+        <v>18</v>
+      </c>
+      <c r="G666" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H666" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="667" customHeight="1" spans="1:8">
+      <c r="A667" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B667" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C667" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D667" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E667" s="1">
+        <v>93.1</v>
+      </c>
+      <c r="F667" s="1">
+        <v>17.6</v>
+      </c>
+      <c r="G667" s="1">
+        <v>91.3</v>
+      </c>
+      <c r="H667" s="1">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="668" customHeight="1" spans="1:8">
+      <c r="A668" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B668" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C668" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D668" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E668" s="1">
+        <v>84.6</v>
+      </c>
+      <c r="F668" s="1">
+        <v>15.6</v>
+      </c>
+      <c r="G668" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H668" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="669" customHeight="1" spans="1:8">
+      <c r="A669" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B669" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C669" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D669" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E669" s="1">
+        <v>86.7</v>
+      </c>
+      <c r="F669" s="1">
+        <v>15.1</v>
+      </c>
+      <c r="G669" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H669" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="670" customHeight="1" spans="1:8">
+      <c r="A670" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B670" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C670" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D670" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E670" s="1">
+        <v>75.9</v>
+      </c>
+      <c r="F670" s="1">
+        <v>14.8</v>
+      </c>
+      <c r="G670" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H670" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="671" customHeight="1" spans="1:8">
+      <c r="A671" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B671" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C671" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D671" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E671" s="1">
+        <v>86.8</v>
+      </c>
+      <c r="F671" s="1">
+        <v>13.3</v>
+      </c>
+      <c r="G671" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H671" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="672" customHeight="1" spans="1:8">
+      <c r="A672" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B672" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C672" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D672" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E672" s="1">
+        <v>62.4</v>
+      </c>
+      <c r="F672" s="1">
+        <v>12.8</v>
+      </c>
+      <c r="G672" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H672" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="673" customHeight="1" spans="1:8">
+      <c r="A673" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B673" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C673" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D673" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E673" s="1">
+        <v>119.9</v>
+      </c>
+      <c r="F673" s="1">
+        <v>12.6</v>
+      </c>
+      <c r="G673" s="1">
+        <v>91.3</v>
+      </c>
+      <c r="H673" s="1">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="674" customHeight="1" spans="1:8">
+      <c r="A674" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B674" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C674" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D674" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E674" s="1">
+        <v>71.8</v>
+      </c>
+      <c r="F674" s="1">
+        <v>11.5</v>
+      </c>
+      <c r="G674" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H674" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="675" customHeight="1" spans="1:8">
+      <c r="A675" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B675" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C675" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D675" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E675" s="1">
+        <v>103.6</v>
+      </c>
+      <c r="F675" s="1">
+        <v>10.9</v>
+      </c>
+      <c r="G675" s="1">
+        <v>91.3</v>
+      </c>
+      <c r="H675" s="1">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="676" customHeight="1" spans="1:8">
+      <c r="A676" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B676" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C676" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D676" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E676" s="1">
+        <v>163.4</v>
+      </c>
+      <c r="F676" s="1">
+        <v>10.6</v>
+      </c>
+      <c r="G676" s="1">
+        <v>91.3</v>
+      </c>
+      <c r="H676" s="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="677" customHeight="1" spans="1:8">
+      <c r="A677" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B677" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C677" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D677" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E677" s="1">
+        <v>109.8</v>
+      </c>
+      <c r="F677" s="1">
+        <v>9.8</v>
+      </c>
+      <c r="G677" s="1">
+        <v>91.3</v>
+      </c>
+      <c r="H677" s="1">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="678" customHeight="1" spans="1:8">
+      <c r="A678" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C678" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D678" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E678" s="1">
+        <v>118.6</v>
+      </c>
+      <c r="F678" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="G678" s="1">
+        <v>91.3</v>
+      </c>
+      <c r="H678" s="1">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="679" customHeight="1" spans="1:8">
+      <c r="A679" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B679" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C679" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D679" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E679" s="1">
+        <v>105.1</v>
+      </c>
+      <c r="F679" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="G679" s="1">
+        <v>91.3</v>
+      </c>
+      <c r="H679" s="1">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="680" customHeight="1" spans="1:8">
+      <c r="A680" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B680" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C680" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D680" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E680" s="1">
+        <v>114.9</v>
+      </c>
+      <c r="F680" s="1">
+        <v>6</v>
+      </c>
+      <c r="G680" s="1">
+        <v>91.3</v>
+      </c>
+      <c r="H680" s="1">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="681" customHeight="1" spans="1:8">
+      <c r="A681" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B681" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C681" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D681" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E681" s="1">
+        <v>100.6</v>
+      </c>
+      <c r="F681" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="G681" s="1">
+        <v>91.3</v>
+      </c>
+      <c r="H681" s="1">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="682" customHeight="1" spans="1:8">
+      <c r="A682" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B682" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C682" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D682" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E682" s="1">
+        <v>102.7</v>
+      </c>
+      <c r="F682" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="G682" s="1">
+        <v>91.3</v>
+      </c>
+      <c r="H682" s="1">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="683" customHeight="1" spans="1:8">
+      <c r="A683" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B683" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C683" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D683" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E683" s="1">
+        <v>100.6</v>
+      </c>
+      <c r="F683" s="1">
+        <v>2.3</v>
+      </c>
+      <c r="G683" s="1">
+        <v>91.3</v>
+      </c>
+      <c r="H683" s="1">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="684" customHeight="1" spans="1:8">
+      <c r="A684" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B684" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C684" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D684" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E684" s="1">
+        <v>107.6</v>
+      </c>
+      <c r="F684" s="1">
+        <v>1.1</v>
+      </c>
+      <c r="G684" s="1">
+        <v>91.3</v>
+      </c>
+      <c r="H684" s="1">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="685" customHeight="1" spans="1:8">
+      <c r="A685" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B685" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C685" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D685" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E685" s="1">
+        <v>107.5</v>
+      </c>
+      <c r="F685" s="1">
+        <v>-0.1</v>
+      </c>
+      <c r="G685" s="1">
+        <v>91.3</v>
+      </c>
+      <c r="H685" s="1">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="686" customHeight="1" spans="1:8">
+      <c r="A686" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B686" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C686" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D686" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E686" s="1">
+        <v>112.9</v>
+      </c>
+      <c r="F686" s="1">
+        <v>-1.2</v>
+      </c>
+      <c r="G686" s="1">
+        <v>91.3</v>
+      </c>
+      <c r="H686" s="1">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="687" customHeight="1" spans="1:8">
+      <c r="A687" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B687" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C687" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D687" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E687" s="1">
+        <v>102.4</v>
+      </c>
+      <c r="F687" s="1">
+        <v>-5.6</v>
+      </c>
+      <c r="G687" s="1">
+        <v>91.3</v>
+      </c>
+      <c r="H687" s="1">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="688" customHeight="1" spans="1:8">
+      <c r="A688" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B688" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C688" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D688" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E688" s="1">
+        <v>73.4</v>
+      </c>
+      <c r="F688" s="1">
+        <v>19.3</v>
+      </c>
+      <c r="G688" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H688" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="689" customHeight="1" spans="1:8">
+      <c r="A689" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B689" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C689" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D689" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E689" s="1">
+        <v>47.5</v>
+      </c>
+      <c r="F689" s="1">
+        <v>18.2</v>
+      </c>
+      <c r="G689" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H689" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="690" customHeight="1" spans="1:8">
+      <c r="A690" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B690" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C690" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D690" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E690" s="1">
+        <v>88.6</v>
+      </c>
+      <c r="F690" s="1">
+        <v>17.8</v>
+      </c>
+      <c r="G690" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H690" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="691" customHeight="1" spans="1:8">
+      <c r="A691" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B691" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C691" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D691" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E691" s="1">
+        <v>93</v>
+      </c>
+      <c r="F691" s="1">
+        <v>17.6</v>
+      </c>
+      <c r="G691" s="1">
+        <v>91.2</v>
+      </c>
+      <c r="H691" s="1">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="692" customHeight="1" spans="1:8">
+      <c r="A692" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B692" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C692" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D692" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E692" s="1">
+        <v>86.8</v>
+      </c>
+      <c r="F692" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="G692" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H692" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="693" customHeight="1" spans="1:8">
+      <c r="A693" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B693" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C693" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D693" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E693" s="1">
+        <v>84.2</v>
+      </c>
+      <c r="F693" s="1">
+        <v>15.1</v>
+      </c>
+      <c r="G693" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H693" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="694" customHeight="1" spans="1:8">
+      <c r="A694" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B694" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C694" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D694" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E694" s="1">
+        <v>75.8</v>
+      </c>
+      <c r="F694" s="1">
+        <v>14.6</v>
+      </c>
+      <c r="G694" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H694" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="695" customHeight="1" spans="1:8">
+      <c r="A695" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B695" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C695" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D695" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E695" s="1">
+        <v>72.9</v>
+      </c>
+      <c r="F695" s="1">
+        <v>13.4</v>
+      </c>
+      <c r="G695" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H695" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="696" customHeight="1" spans="1:8">
+      <c r="A696" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B696" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C696" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D696" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E696" s="1">
+        <v>86.8</v>
+      </c>
+      <c r="F696" s="1">
+        <v>13.3</v>
+      </c>
+      <c r="G696" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H696" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="697" customHeight="1" spans="1:8">
+      <c r="A697" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B697" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C697" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D697" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E697" s="1">
+        <v>119.9</v>
+      </c>
+      <c r="F697" s="1">
+        <v>12.7</v>
+      </c>
+      <c r="G697" s="1">
+        <v>91.2</v>
+      </c>
+      <c r="H697" s="1">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="698" customHeight="1" spans="1:8">
+      <c r="A698" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B698" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C698" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D698" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E698" s="1">
+        <v>62.4</v>
+      </c>
+      <c r="F698" s="1">
+        <v>12.7</v>
+      </c>
+      <c r="G698" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H698" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="699" customHeight="1" spans="1:8">
+      <c r="A699" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B699" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C699" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D699" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E699" s="1">
+        <v>103.6</v>
+      </c>
+      <c r="F699" s="1">
+        <v>10.9</v>
+      </c>
+      <c r="G699" s="1">
+        <v>91.2</v>
+      </c>
+      <c r="H699" s="1">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="700" customHeight="1" spans="1:8">
+      <c r="A700" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B700" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C700" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D700" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E700" s="1">
+        <v>163.4</v>
+      </c>
+      <c r="F700" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="G700" s="1">
+        <v>91.2</v>
+      </c>
+      <c r="H700" s="1">
+        <v>79.1</v>
+      </c>
+    </row>
+    <row r="701" customHeight="1" spans="1:8">
+      <c r="A701" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B701" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C701" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D701" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E701" s="1">
+        <v>109.6</v>
+      </c>
+      <c r="F701" s="1">
+        <v>9.6</v>
+      </c>
+      <c r="G701" s="1">
+        <v>91.2</v>
+      </c>
+      <c r="H701" s="1">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="702" customHeight="1" spans="1:8">
+      <c r="A702" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B702" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C702" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D702" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E702" s="1">
+        <v>118.8</v>
+      </c>
+      <c r="F702" s="1">
+        <v>8.8</v>
+      </c>
+      <c r="G702" s="1">
+        <v>91.2</v>
+      </c>
+      <c r="H702" s="1">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="703" customHeight="1" spans="1:8">
+      <c r="A703" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B703" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C703" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D703" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E703" s="1">
+        <v>105</v>
+      </c>
+      <c r="F703" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="G703" s="1">
+        <v>91.2</v>
+      </c>
+      <c r="H703" s="1">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="704" customHeight="1" spans="1:8">
+      <c r="A704" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B704" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C704" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D704" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E704" s="1">
+        <v>114.7</v>
+      </c>
+      <c r="F704" s="1">
+        <v>5.8</v>
+      </c>
+      <c r="G704" s="1">
+        <v>91.2</v>
+      </c>
+      <c r="H704" s="1">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="705" customHeight="1" spans="1:8">
+      <c r="A705" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B705" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C705" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D705" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E705" s="1">
+        <v>100.5</v>
+      </c>
+      <c r="F705" s="1">
+        <v>4.4</v>
+      </c>
+      <c r="G705" s="1">
+        <v>91.2</v>
+      </c>
+      <c r="H705" s="1">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="706" customHeight="1" spans="1:8">
+      <c r="A706" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B706" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C706" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D706" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E706" s="1">
+        <v>102.7</v>
+      </c>
+      <c r="F706" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="G706" s="1">
+        <v>91.2</v>
+      </c>
+      <c r="H706" s="1">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="707" customHeight="1" spans="1:8">
+      <c r="A707" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B707" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C707" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D707" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E707" s="1">
+        <v>100.5</v>
+      </c>
+      <c r="F707" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="G707" s="1">
+        <v>91.2</v>
+      </c>
+      <c r="H707" s="1">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="708" customHeight="1" spans="1:8">
+      <c r="A708" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B708" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C708" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D708" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E708" s="1">
+        <v>107.5</v>
+      </c>
+      <c r="F708" s="1">
+        <v>1</v>
+      </c>
+      <c r="G708" s="1">
+        <v>91.2</v>
+      </c>
+      <c r="H708" s="1">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="709" customHeight="1" spans="1:8">
+      <c r="A709" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B709" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C709" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D709" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E709" s="1">
+        <v>107.4</v>
+      </c>
+      <c r="F709" s="1">
+        <v>-0.2</v>
+      </c>
+      <c r="G709" s="1">
+        <v>91.2</v>
+      </c>
+      <c r="H709" s="1">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="710" customHeight="1" spans="1:8">
+      <c r="A710" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B710" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C710" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D710" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E710" s="1">
+        <v>112.7</v>
+      </c>
+      <c r="F710" s="1">
+        <v>-1.3</v>
+      </c>
+      <c r="G710" s="1">
+        <v>91.2</v>
+      </c>
+      <c r="H710" s="1">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="711" customHeight="1" spans="1:8">
+      <c r="A711" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B711" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C711" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D711" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E711" s="1">
+        <v>102.3</v>
+      </c>
+      <c r="F711" s="1">
+        <v>-5.7</v>
+      </c>
+      <c r="G711" s="1">
+        <v>91.2</v>
+      </c>
+      <c r="H711" s="1">
+        <v>12.1</v>
       </c>
     </row>
   </sheetData>
